--- a/dados/SURVEY_BRAM_D2.xlsx
+++ b/dados/SURVEY_BRAM_D2.xlsx
@@ -3236,7 +3236,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -4172,7 +4172,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -5050,7 +5050,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -7800,7 +7800,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Underway Using Engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Underway</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K18" t="n">

--- a/dados/SURVEY_BRAM_D2.xlsx
+++ b/dados/SURVEY_BRAM_D2.xlsx
@@ -544,7 +544,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -1480,7 +1480,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -2358,7 +2358,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>restricted manoeuvrability</t>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -5986,7 +5986,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>restricted manoeuvrability</t>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -8828,7 +8828,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -9764,7 +9764,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>restricted manoeuvrability</t>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>restricted manoeuvrability</t>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -10644,7 +10644,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At anchor</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -11580,7 +11580,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -12458,7 +12458,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K3" t="n">

--- a/dados/SURVEY_BRAM_D2.xlsx
+++ b/dados/SURVEY_BRAM_D2.xlsx
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>30.333</v>
+        <v>23.522</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PNA-1</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Fixa (Habitada)</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>namorado</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -9180,25 +9180,25 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>27.901</v>
+        <v>4.367</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.002777777777777778</v>

--- a/dados/SURVEY_BRAM_D2.xlsx
+++ b/dados/SURVEY_BRAM_D2.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1482,6 +1482,64 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>0.00625</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2.361111111111111</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46233.70625</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1.415972222222222</v>
+      </c>
+      <c r="E19" t="n">
+        <v>82.28</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G19" t="n">
+        <v>33.98333333333333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>77.943</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.9513888888888888</v>
       </c>
     </row>
   </sheetData>
@@ -1495,7 +1553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2476,6 +2534,64 @@
       </c>
       <c r="P17" s="3" t="n">
         <v>0.007638888888888889</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2.361111111111111</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46234.64861111111</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2.359722222222222</v>
+      </c>
+      <c r="E18" t="n">
+        <v>313.4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G18" t="n">
+        <v>56.63333333333333</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0.009027777777777777</v>
       </c>
     </row>
   </sheetData>
@@ -2489,7 +2605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3470,6 +3586,64 @@
       </c>
       <c r="P17" s="3" t="n">
         <v>5.845138888888889</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2.348611111111111</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46226.45902777778</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>56.36666666666667</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>5.566</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Porto de imbetiba</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>porto macae</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>8.19375</v>
       </c>
     </row>
   </sheetData>
@@ -3483,7 +3657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4522,6 +4696,64 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>0.003472222222222222</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2.348611111111111</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46232.78472222222</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0.4840277777777778</v>
+      </c>
+      <c r="E19" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.36666666666667</v>
+      </c>
+      <c r="G19" t="n">
+        <v>11.61666666666667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>51.458</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>1.868055555555556</v>
       </c>
     </row>
   </sheetData>
@@ -4535,7 +4767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5516,6 +5748,64 @@
       </c>
       <c r="P17" s="3" t="n">
         <v>0.003472222222222222</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2.348611111111111</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46233.2125</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0.9118055555555555</v>
+      </c>
+      <c r="E18" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="F18" t="n">
+        <v>56.36666666666667</v>
+      </c>
+      <c r="G18" t="n">
+        <v>21.88333333333333</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>46.626</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>1.440277777777778</v>
       </c>
     </row>
   </sheetData>
@@ -5529,7 +5819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6568,6 +6858,64 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>0.008333333333333333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2.348611111111111</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46232.60555555556</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0.3097222222222222</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.36666666666667</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.433333333333334</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>8.018000000000001</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>P-78</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>2.047222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -6581,7 +6929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7562,6 +7910,60 @@
       </c>
       <c r="P17" s="3" t="n">
         <v>0.007638888888888889</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2.361111111111111</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46233.65694444445</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1.368055555555556</v>
+      </c>
+      <c r="E18" t="n">
+        <v>169.89</v>
+      </c>
+      <c r="F18" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G18" t="n">
+        <v>32.83333333333334</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6.797</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>FPSO ANNA NERY</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>1.000694444444445</v>
       </c>
     </row>
   </sheetData>
@@ -7575,7 +7977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8614,6 +9016,64 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>0.04513888888888889</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2.361111111111111</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46232.57083333333</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0.3194444444444444</v>
+      </c>
+      <c r="E19" t="n">
+        <v>37.61</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>18.568</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>PETROBRAS 68 (P-68)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>berbigao</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>2.086805555555555</v>
       </c>
     </row>
   </sheetData>
@@ -8627,7 +9087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9757,6 +10217,64 @@
         <v>1</v>
       </c>
       <c r="P20" s="3" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.361111111111111</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.65555555555</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.361111111111111</v>
+      </c>
+      <c r="E21" t="n">
+        <v>96.48999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G21" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Porto de imbetiba</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>porto macae</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>0.002083333333333333</v>
       </c>
     </row>
@@ -9771,7 +10289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10810,6 +11328,64 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2.361111111111111</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46234.61736111111</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2.322222222222222</v>
+      </c>
+      <c r="E19" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55.73333333333333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>20.759</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.04027777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -10823,7 +11399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11854,6 +12430,64 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2118055555555556</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2.361111111111111</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46234.61666666667</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2.531944444444445</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60.76666666666667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>3.442</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>BRAVA STAR</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>jubarte</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.04097222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -11867,7 +12501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12906,6 +13540,64 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>0.1013888888888889</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2.361111111111111</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46234.64791666667</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2.452777777777778</v>
+      </c>
+      <c r="E19" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G19" t="n">
+        <v>58.86666666666667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>P-79</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.009722222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -12919,7 +13611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13900,6 +14592,64 @@
       </c>
       <c r="P17" s="3" t="n">
         <v>0.008333333333333333</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2.361111111111111</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46232.60069444445</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="E18" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="F18" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>42.603</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PETROBRAS 68 (P-68)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>berbigao</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>2.056944444444444</v>
       </c>
     </row>
   </sheetData>
@@ -13913,7 +14663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14898,6 +15648,60 @@
         <v>0.002777777777777778</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2.361111111111111</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46234.65416666667</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2.360416666666667</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="G19" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>ATLANTIC STAR (SS45)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.003472222222222222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados/SURVEY_BRAM_D2.xlsx
+++ b/dados/SURVEY_BRAM_D2.xlsx
@@ -2396,11 +2396,11 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>7.731</v>
+        <v>1.264</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>PETROBRAS 66 (P-66)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.01319444444444444</v>
@@ -2454,11 +2454,11 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>7.195</v>
+        <v>0.074</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>PETROBRAS 66 (P-66)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>0.02430555555555556</v>
@@ -8994,11 +8994,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>15.118</v>
+        <v>11.81</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>PETROBRAS 67 (P-67)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -10668,11 +10668,11 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>39.579</v>
+        <v>30.639</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PETROBRAS 71 (P-71)</t>
+          <t>FPSO CIDADE ITAGUAI</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>itapu</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -10726,11 +10726,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>39.579</v>
+        <v>30.639</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PETROBRAS 71 (P-71)</t>
+          <t>FPSO CIDADE ITAGUAI</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>itapu</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -10784,11 +10784,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>39.579</v>
+        <v>30.639</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PETROBRAS 71 (P-71)</t>
+          <t>FPSO CIDADE ITAGUAI</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>itapu</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -10842,11 +10842,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>39.579</v>
+        <v>30.639</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PETROBRAS 71 (P-71)</t>
+          <t>FPSO CIDADE ITAGUAI</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>itapu</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -10900,11 +10900,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>39.579</v>
+        <v>30.639</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PETROBRAS 71 (P-71)</t>
+          <t>FPSO CIDADE ITAGUAI</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>itapu</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -10958,11 +10958,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>39.579</v>
+        <v>30.639</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PETROBRAS 71 (P-71)</t>
+          <t>FPSO CIDADE ITAGUAI</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>itapu</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -11016,11 +11016,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>39.579</v>
+        <v>30.639</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PETROBRAS 71 (P-71)</t>
+          <t>FPSO CIDADE ITAGUAI</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>itapu</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -11074,11 +11074,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>39.579</v>
+        <v>30.639</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PETROBRAS 71 (P-71)</t>
+          <t>FPSO CIDADE ITAGUAI</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>itapu</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -11132,11 +11132,11 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>39.579</v>
+        <v>30.639</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PETROBRAS 71 (P-71)</t>
+          <t>FPSO CIDADE ITAGUAI</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>itapu</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -14628,11 +14628,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>42.603</v>
+        <v>13.201</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>FPSO CIDADE ITAGUAI</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O18" t="n">

--- a/dados/SURVEY_BRAM_D2.xlsx
+++ b/dados/SURVEY_BRAM_D2.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1540,6 +1540,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.9513888888888888</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46233.70625</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>77.943</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>1.699305555555556</v>
       </c>
     </row>
   </sheetData>
@@ -1553,7 +1611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2592,6 +2650,64 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>0.009027777777777777</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0.7548611111111111</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="G19" t="n">
+        <v>18.11666666666667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.002083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2605,7 +2721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3644,6 +3760,60 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>8.19375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0.7673611111111112</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46234.7875</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>8.328472222222222</v>
+      </c>
+      <c r="E19" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>18.41666666666667</v>
+      </c>
+      <c r="G19" t="n">
+        <v>199.8833333333333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5.927</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>FPSO ANNA NERY</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.6326388888888889</v>
       </c>
     </row>
   </sheetData>
@@ -3657,7 +3827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4754,6 +4924,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>1.868055555555556</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.7673611111111112</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46232.78472222222</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>18.41666666666667</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>51.458</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>2.635416666666667</v>
       </c>
     </row>
   </sheetData>
@@ -4767,7 +4995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5806,6 +6034,64 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>1.440277777777778</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0.7673611111111112</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46233.2125</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>18.41666666666667</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>46.626</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>2.207638888888889</v>
       </c>
     </row>
   </sheetData>
@@ -5819,7 +6105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6916,6 +7202,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>2.047222222222222</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.7673611111111112</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46232.60555555556</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>18.41666666666667</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>8.018000000000001</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>P-78</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>2.814583333333333</v>
       </c>
     </row>
   </sheetData>
@@ -6929,7 +7273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7964,6 +8308,60 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>1.000694444444445</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46234.7875</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1.130555555555556</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="G19" t="n">
+        <v>27.13333333333333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>7.696</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>FPSO ANNA NERY</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.6180555555555556</v>
       </c>
     </row>
   </sheetData>
@@ -7977,7 +8375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8182,21 +8580,21 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8.868</v>
+        <v>8.507999999999999</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>NORBE IX</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>navio sonda</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -8240,25 +8638,25 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6.368</v>
+        <v>2.828</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>NORBE IX</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>navio sonda</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.06805555555555555</v>
@@ -8298,25 +8696,25 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.368</v>
+        <v>2.828</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>NORBE IX</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>navio sonda</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.4534721643518519</v>
@@ -8356,25 +8754,25 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3.848</v>
+        <v>0.046</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>NORBE IX</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>navio sonda</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.1611111111111111</v>
@@ -8414,25 +8812,25 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3.873</v>
+        <v>0.051</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>NORBE IX</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>navio sonda</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0</v>
@@ -8472,25 +8870,25 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3.877</v>
+        <v>0.052</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>NORBE IX</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>navio sonda</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.5305555555555556</v>
@@ -8530,25 +8928,25 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3.877</v>
+        <v>0.052</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>NORBE IX</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>navio sonda</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.9201388888888888</v>
@@ -8588,25 +8986,25 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3.877</v>
+        <v>0.052</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>NORBE IX</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>navio sonda</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>1.517361111111111</v>
@@ -8646,25 +9044,25 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3.877</v>
+        <v>0.052</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>NORBE IX</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>navio sonda</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.898611111111111</v>
@@ -9052,11 +9450,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>18.568</v>
+        <v>3.227</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PETROBRAS 68 (P-68)</t>
+          <t>PETROBRAS 70 (P-70)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9066,14 +9464,72 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>berbigao</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>2.086805555555555</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46232.57083333333</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PETROBRAS 70 (P-70)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>atapu</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>2.834722222222222</v>
       </c>
     </row>
   </sheetData>
@@ -9087,7 +9543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10276,6 +10732,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.7451388888888889</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="G22" t="n">
+        <v>17.88333333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Porto de imbetiba</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>porto macae</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.004861111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -10289,7 +10803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10436,25 +10950,25 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11.181</v>
+        <v>8.239000000000001</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>NORBE IX</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>navio sonda</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>atapu</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>2.927777777777778</v>
@@ -11386,6 +11900,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.04027777777777778</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46234.69166666667</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.07430555555555556</v>
+      </c>
+      <c r="E20" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.783333333333333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>49.181</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.7138888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -11399,7 +11971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11546,11 +12118,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.231</v>
+        <v>1.382</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEEPWATER ÁQUILA </t>
+          <t>NORBE VI</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -11558,11 +12130,7 @@
           <t>navio sonda</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>jubarte</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
         <v>0.8</v>
       </c>
@@ -11770,23 +12338,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.516</v>
+        <v>1.303</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BRAVA STAR</t>
+          <t>NORBE VI</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Semi-Sub/Perfuração</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>jubarte</t>
-        </is>
-      </c>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
         <v>0.8</v>
       </c>
@@ -11828,23 +12392,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1.525</v>
+        <v>1.295</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BRAVA STAR</t>
+          <t>NORBE VI</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Semi-Sub/Perfuração</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>jubarte</t>
-        </is>
-      </c>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
         <v>0.8</v>
       </c>
@@ -11886,23 +12446,19 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1.499</v>
+        <v>1.304</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BRAVA STAR</t>
+          <t>NORBE VI</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Semi-Sub/Perfuração</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>jubarte</t>
-        </is>
-      </c>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
         <v>0.8</v>
       </c>
@@ -11944,23 +12500,19 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1.499</v>
+        <v>1.304</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BRAVA STAR</t>
+          <t>NORBE VI</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Semi-Sub/Perfuração</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>jubarte</t>
-        </is>
-      </c>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
         <v>0.8</v>
       </c>
@@ -12350,25 +12902,21 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>3.509</v>
+        <v>2.312</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BRAVA STAR</t>
+          <t>NORBE VI</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Semi-Sub/Perfuração</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>jubarte</t>
-        </is>
-      </c>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.1361111111111111</v>
@@ -12408,25 +12956,21 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3.474</v>
+        <v>2.331</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BRAVA STAR</t>
+          <t>NORBE VI</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Semi-Sub/Perfuração</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>jubarte</t>
-        </is>
-      </c>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2118055555555556</v>
@@ -12466,28 +13010,78 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3.442</v>
+        <v>2.178</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BRAVA STAR</t>
+          <t>NORBE VI</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Semi-Sub/Perfuração</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>jubarte</t>
-        </is>
-      </c>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.04097222222222222</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46234.67222222222</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>2.164</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NORBE VI</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.7333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -12501,7 +13095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13598,6 +14192,60 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.009722222222222222</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.7555555555555555</v>
+      </c>
+      <c r="E20" t="n">
+        <v>157.16</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>18.13333333333333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ATLANTIC STAR (SS45)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.002083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -13611,7 +14259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14650,6 +15298,64 @@
       </c>
       <c r="P18" s="3" t="n">
         <v>2.056944444444444</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46232.60069444445</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>13.201</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>FPSO CIDADE ITAGUAI</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>tupi</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>2.804861111111111</v>
       </c>
     </row>
   </sheetData>
@@ -14663,7 +15369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15702,6 +16408,64 @@
         <v>0.003472222222222222</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.7479166666666667</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46235.40416666667</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>18</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados/SURVEY_BRAM_D2.xlsx
+++ b/dados/SURVEY_BRAM_D2.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,6 +1598,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>1.699305555555556</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46236.35347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46236.2</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.49375</v>
+      </c>
+      <c r="E21" t="n">
+        <v>141.42</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>8.957000000000001</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>P-78</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.1534722222222222</v>
       </c>
     </row>
   </sheetData>
@@ -1611,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2708,6 +2766,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46236.35347222222</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46236.34583333333</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.9423611111111111</v>
+      </c>
+      <c r="E20" t="n">
+        <v>147.39</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G20" t="n">
+        <v>22.61666666666667</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>68.655</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>almirante barroso_FSO</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.007638888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -2721,7 +2837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3814,6 +3930,60 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.6326388888888889</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46236.34930555556</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.9291666666666667</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46234.7875</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5.927</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>FPSO ANNA NERY</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>1.561805555555555</v>
       </c>
     </row>
   </sheetData>
@@ -3827,7 +3997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4982,6 +5152,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>2.635416666666667</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46236.34930555556</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9291666666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46236.27291666667</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3.488194444444444</v>
+      </c>
+      <c r="E21" t="n">
+        <v>155.57</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>83.71666666666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6.151</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>P-77_FSO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.0763888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -4995,7 +5223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6092,6 +6320,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>2.207638888888889</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46236.34930555556</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.9291666666666667</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46233.2125</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>46.626</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>3.136805555555556</v>
       </c>
     </row>
   </sheetData>
@@ -6105,7 +6391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7260,6 +7546,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>2.814583333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46236.34930555556</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9291666666666667</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46232.60555555556</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>8.018000000000001</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>P-78</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>3.74375</v>
       </c>
     </row>
   </sheetData>
@@ -7273,7 +7617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8362,6 +8706,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.6180555555555556</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46236.35347222222</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46235.69583333333</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.9083333333333333</v>
+      </c>
+      <c r="E20" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G20" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PETROBRAS 31 (P-31)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>albacora</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.6576388888888889</v>
       </c>
     </row>
   </sheetData>
@@ -8375,7 +8777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9530,6 +9932,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>2.834722222222222</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46236.35347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46232.57083333333</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PETROBRAS 70 (P-70)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>atapu</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>3.782638888888889</v>
       </c>
     </row>
   </sheetData>
@@ -9543,7 +10003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10790,6 +11250,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.004861111111111111</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.35347222222</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.32152777778</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9208333333333333</v>
+      </c>
+      <c r="E23" t="n">
+        <v>186.33</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>10.733</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PETROBRAS 31 (P-31)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>albacora</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.03194444444444444</v>
       </c>
     </row>
   </sheetData>
@@ -10803,7 +11321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11958,6 +12476,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.7138888888888889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46236.35347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.69166666667</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>49.181</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1.661805555555556</v>
       </c>
     </row>
   </sheetData>
@@ -11971,7 +12547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13082,6 +13658,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.7333333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46236.35347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46236.22569444445</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1.553472222222222</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>37.28333333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BRAVA STAR</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>jubarte</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.1277777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -13095,7 +13729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14246,6 +14880,60 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46236.35347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46236.35</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.9465277777777777</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>22.71666666666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>ATLANTIC STAR (SS45)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.003472222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -14259,7 +14947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15356,6 +16044,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>2.804861111111111</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46236.35347222222</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46236.21944444445</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3.61875</v>
+      </c>
+      <c r="E20" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G20" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>3.978</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>FPSO CIDADE ITAGUAI</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>tupi</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.1340277777777778</v>
       </c>
     </row>
   </sheetData>
@@ -15369,7 +16115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16466,6 +17212,64 @@
         <v>0.001388888888888889</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46236.35347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46236.34791666667</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.94375</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G21" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.005555555555555556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados/SURVEY_BRAM_D2.xlsx
+++ b/dados/SURVEY_BRAM_D2.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1656,6 +1656,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.1534722222222222</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9805555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.99375</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.79375</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>P-78</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.3402777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -1669,7 +1727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2824,6 +2882,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.007638888888888889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9805555555555555</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46236.99722222222</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.6513888888888889</v>
+      </c>
+      <c r="E21" t="n">
+        <v>174.38</v>
+      </c>
+      <c r="F21" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>15.63333333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>9.872999999999999</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PETROBRAS 69 (P-69)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>tupi</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.3368055555555556</v>
       </c>
     </row>
   </sheetData>
@@ -2837,7 +2953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3984,6 +4100,60 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>1.561805555555555</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9847222222222223</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.7875</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>23.63333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>5.927</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>FPSO ANNA NERY</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.546527777777778</v>
       </c>
     </row>
   </sheetData>
@@ -3997,7 +4167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5210,6 +5380,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.0763888888888889</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9847222222222223</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.93055555555</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.6576388888888889</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.63333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15.78333333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>P-77_FSO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.4034722222222222</v>
       </c>
     </row>
   </sheetData>
@@ -5223,7 +5451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6378,6 +6606,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>3.136805555555556</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9847222222222223</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46236.81041666667</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>3.597916666666667</v>
+      </c>
+      <c r="E21" t="n">
+        <v>236.46</v>
+      </c>
+      <c r="F21" t="n">
+        <v>23.63333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>86.34999999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>3.686</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>FPSO CIDADE PARATY</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>tupi</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.5236111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7604,6 +7890,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>3.74375</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9847222222222223</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.93541666667</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>4.329861111111111</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.63333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>103.9166666666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>4.604</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>P-78</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.3986111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -7617,7 +7961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8764,6 +9108,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.6576388888888889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9805555555555555</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46237.32986111111</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1.634027777777778</v>
+      </c>
+      <c r="E21" t="n">
+        <v>113.31</v>
+      </c>
+      <c r="F21" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>39.21666666666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NOV Flexiveis</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>porto açu</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.004166666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -8777,7 +9179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9990,6 +10392,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>3.782638888888889</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9805555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.77361111111</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>4.202777777777778</v>
+      </c>
+      <c r="E22" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>100.8666666666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>8.403</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>FPSO CIDADE MANGARATIBA</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>tupi</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.5604166666666667</v>
       </c>
     </row>
   </sheetData>
@@ -10003,7 +10463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11308,6 +11768,64 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.03194444444444444</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9805555555555555</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.31875</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.9972222222222222</v>
+      </c>
+      <c r="E24" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23.93333333333333</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Underway</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>12.221</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PETROBRAS 31 (P-31)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>albacora</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.01527777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -11321,7 +11839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12534,6 +13052,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>1.661805555555556</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9805555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46234.69166666667</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>49.181</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.642361111111111</v>
       </c>
     </row>
   </sheetData>
@@ -12547,7 +13123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13716,6 +14292,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.1277777777777778</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9805555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46237.32569444444</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BRAVA STAR</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>jubarte</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.008333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -13729,7 +14363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14934,6 +15568,60 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.003472222222222222</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9805555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46237.32708333333</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.9770833333333333</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ATLANTIC STAR (SS45)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.006944444444444444</v>
       </c>
     </row>
   </sheetData>
@@ -14947,7 +15635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16102,6 +16790,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.1340277777777778</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.9805555555555555</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46237.32777777778</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1.108333333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>254.13</v>
+      </c>
+      <c r="F21" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.00625</v>
       </c>
     </row>
   </sheetData>
@@ -16115,7 +16861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17270,6 +18016,64 @@
         <v>0.005555555555555556</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9805555555555555</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46237.32708333333</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.53333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.006944444444444444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
